--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:26:54+00:00</t>
+    <t>2025-01-23T13:26:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="202">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Personne physique</t>
+    <t>L'élément de l'en-tête du CDA patient permet de représenter une personne physique.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -416,6 +416,106 @@
 </t>
   </si>
   <si>
+    <t>Noms et prénoms.</t>
+  </si>
+  <si>
+    <t>Patient.name.nullFlavor</t>
+  </si>
+  <si>
+    <t>Patient.name.use</t>
+  </si>
+  <si>
+    <t>Use Code</t>
+  </si>
+  <si>
+    <t>A set of codes advising a system or user which name in a set of like names to select for a given purpose. A name without specific use code might be a default name useful for any purpose, but a name with a specific use code would be preferred for that respective purpose</t>
+  </si>
+  <si>
+    <t>http://hl7.org/cda/stds/core/ValueSet/CDAEntityNameUse</t>
+  </si>
+  <si>
+    <t>EN.use</t>
+  </si>
+  <si>
+    <t>Patient.name.item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base
+</t>
+  </si>
+  <si>
+    <t>A series of items that constitute the name.</t>
+  </si>
+  <si>
+    <t>EN.item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EN-1:Can only have only one of the possible item elements in each choice {(delimiter | family | given | prefix | suffix | xmlText).count() = 1}
+</t>
+  </si>
+  <si>
+    <t>Patient.name.item.delimiter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ENXP
+</t>
+  </si>
+  <si>
+    <t>EN.item.delimiter</t>
+  </si>
+  <si>
+    <t>Patient.name.item.family</t>
+  </si>
+  <si>
+    <t>EN.item.family</t>
+  </si>
+  <si>
+    <t>Patient.name.item.given</t>
+  </si>
+  <si>
+    <t>EN.item.given</t>
+  </si>
+  <si>
+    <t>Patient.name.item.prefix</t>
+  </si>
+  <si>
+    <t>EN.item.prefix</t>
+  </si>
+  <si>
+    <t>Patient.name.item.suffix</t>
+  </si>
+  <si>
+    <t>EN.item.suffix</t>
+  </si>
+  <si>
+    <t>Patient.name.item.xmlText</t>
+  </si>
+  <si>
+    <t>Allows for mixed text content</t>
+  </si>
+  <si>
+    <t>This element is represented in XML as textual content. The actual name "xmlText" will not appear in a CDA instance.</t>
+  </si>
+  <si>
+    <t>EN.item.xmlText</t>
+  </si>
+  <si>
+    <t>Patient.name.validTime</t>
+  </si>
+  <si>
+    <t>Valid Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/IVL-TS
+</t>
+  </si>
+  <si>
+    <t>An interval of time specifying the time during which the name is or was used for the entity. This accomodates the fact that people change names for people, places and things.</t>
+  </si>
+  <si>
+    <t>EN.validTime</t>
+  </si>
+  <si>
     <t>Patient.sdtcDesc</t>
   </si>
   <si>
@@ -433,6 +533,9 @@
 </t>
   </si>
   <si>
+    <t>Sexe.</t>
+  </si>
+  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J143-AdministrativeGender-CISIS/FHIR/JDV-J143-AdministrativeGender-CISIS</t>
   </si>
   <si>
@@ -443,6 +546,9 @@
 </t>
   </si>
   <si>
+    <t>Date de naissance.</t>
+  </si>
+  <si>
     <t>Patient.sdtcDeceasedInd</t>
   </si>
   <si>
@@ -450,10 +556,19 @@
 </t>
   </si>
   <si>
+    <t>Patient décédé ou pas ?</t>
+  </si>
+  <si>
     <t>Patient.sdtcDeceasedTime</t>
   </si>
   <si>
+    <t>Date de décès.</t>
+  </si>
+  <si>
     <t>Patient.sdtcMultipleBirthInd</t>
+  </si>
+  <si>
+    <t>Patient né d'une grossesse multiple.</t>
   </si>
   <si>
     <t>Patient.sdtcMultipleBirthOrderNumber</t>
@@ -463,6 +578,9 @@
 </t>
   </si>
   <si>
+    <t>Numéro d’ordre de naissance (si issu d'une grossesse multiple).</t>
+  </si>
+  <si>
     <t>Patient.maritalStatusCode</t>
   </si>
   <si>
@@ -503,11 +621,17 @@
 </t>
   </si>
   <si>
+    <t>Représentant du patient/usager.</t>
+  </si>
+  <si>
     <t>Patient.birthplace</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Birthplace
 </t>
+  </si>
+  <si>
+    <t>Lieu de naissance.</t>
   </si>
   <si>
     <t>Patient.languageCommunication</t>
@@ -816,7 +940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK31"/>
+  <dimension ref="A1:AK41"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="37.07421875" customWidth="true" bestFit="true"/>
@@ -1091,7 +1215,7 @@
         <v>80</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>74</v>
@@ -2313,7 +2437,9 @@
       <c r="K15" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="L15" s="2"/>
+      <c r="L15" t="s" s="2">
+        <v>131</v>
+      </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2384,21 +2510,23 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E16" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>74</v>
@@ -2410,11 +2538,11 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>133</v>
+        <v>86</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2441,13 +2569,11 @@
         <v>74</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y16" s="2"/>
       <c r="Z16" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>74</v>
@@ -2465,7 +2591,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2485,21 +2611,23 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="F17" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>74</v>
@@ -2511,10 +2639,12 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L17" s="2"/>
+      <c r="M17" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2562,13 +2692,13 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>74</v>
@@ -2582,10 +2712,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2596,7 +2726,7 @@
         <v>75</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>74</v>
@@ -2608,10 +2738,12 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+      <c r="M18" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2661,19 +2793,19 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>74</v>
+        <v>142</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>74</v>
@@ -2681,10 +2813,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2695,7 +2827,7 @@
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>74</v>
@@ -2707,7 +2839,7 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -2760,13 +2892,13 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>74</v>
@@ -2780,10 +2912,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2794,7 +2926,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>74</v>
@@ -2806,7 +2938,7 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -2859,13 +2991,13 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>74</v>
@@ -2879,10 +3011,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2893,7 +3025,7 @@
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>74</v>
@@ -2905,7 +3037,7 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -2958,13 +3090,13 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>74</v>
@@ -2978,10 +3110,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2992,7 +3124,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>74</v>
@@ -3057,13 +3189,13 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>74</v>
@@ -3077,10 +3209,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3091,7 +3223,7 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>74</v>
@@ -3103,7 +3235,7 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -3132,11 +3264,13 @@
         <v>74</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="Y23" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z23" t="s" s="2">
-        <v>147</v>
+        <v>74</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>74</v>
@@ -3154,13 +3288,13 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>74</v>
@@ -3174,10 +3308,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3188,7 +3322,7 @@
         <v>80</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>74</v>
@@ -3200,11 +3334,15 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L24" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>155</v>
+      </c>
       <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
+      <c r="N24" t="s" s="2">
+        <v>156</v>
+      </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>74</v>
@@ -3229,11 +3367,13 @@
         <v>74</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="Y24" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z24" t="s" s="2">
-        <v>149</v>
+        <v>74</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>74</v>
@@ -3251,7 +3391,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3271,21 +3411,23 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E25" s="2"/>
+      <c r="E25" t="s" s="2">
+        <v>159</v>
+      </c>
       <c r="F25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>74</v>
@@ -3297,10 +3439,12 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>135</v>
+        <v>160</v>
       </c>
       <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
+      <c r="M25" t="s" s="2">
+        <v>161</v>
+      </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3326,11 +3470,13 @@
         <v>74</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>74</v>
@@ -3348,7 +3494,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3368,10 +3514,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3382,7 +3528,7 @@
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>74</v>
@@ -3394,10 +3540,12 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
+      <c r="M26" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3423,11 +3571,13 @@
         <v>74</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
@@ -3445,13 +3595,13 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>74</v>
@@ -3465,10 +3615,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3476,10 +3626,10 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>74</v>
@@ -3491,9 +3641,11 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L27" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>168</v>
+      </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3520,11 +3672,11 @@
         <v>74</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>146</v>
+        <v>87</v>
       </c>
       <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>74</v>
@@ -3542,7 +3694,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3562,10 +3714,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3573,10 +3725,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>74</v>
@@ -3588,9 +3740,11 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="L28" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3617,11 +3771,13 @@
         <v>74</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>154</v>
+        <v>74</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>74</v>
@@ -3639,13 +3795,13 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>74</v>
@@ -3659,10 +3815,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3673,7 +3829,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>74</v>
@@ -3685,9 +3841,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="L29" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="M29" s="2"/>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3738,13 +3896,13 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>74</v>
@@ -3758,10 +3916,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3784,9 +3942,11 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="L30" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3837,7 +3997,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -3857,10 +4017,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3871,7 +4031,7 @@
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>74</v>
@@ -3883,9 +4043,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="L31" s="2"/>
+        <v>174</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -3936,21 +4098,1005 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>181</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y33" s="2"/>
+      <c r="Z33" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y34" s="2"/>
+      <c r="Z34" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y35" s="2"/>
+      <c r="Z35" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y36" s="2"/>
+      <c r="Z36" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH36" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ31" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK31" t="s" s="2">
+      <c r="AI36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y37" s="2"/>
+      <c r="Z37" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y38" s="2"/>
+      <c r="Z38" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="C40" s="2"/>
+      <c r="D40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK41" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T15:18:09+00:00</t>
+    <t>2025-02-23T14:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:08:59+00:00</t>
+    <t>2025-02-24T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-patient.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T14:08:41+00:00</t>
+    <t>2025-02-25T09:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
